--- a/uploads/extracted_columns_Unstockit Inventory Template - Copy.xlsx
+++ b/uploads/extracted_columns_Unstockit Inventory Template - Copy.xlsx
@@ -566,7 +566,11 @@
           <t>Manufacturer Warranty</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>uploads\Aruba 70051.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -629,7 +633,11 @@
           <t>Manufacturer Warranty</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>uploads\Aruba 34001.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -690,7 +698,11 @@
           <t>Distributor Warranty</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>uploads\Avoyo cabinet1.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -755,7 +767,11 @@
           <t>No Warranty</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>uploads\9504 24AWG SHIELDED CABLE ACCESS1.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -818,7 +834,11 @@
           <t>Distributor Warranty</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>uploads\54394561.pdf</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/uploads/extracted_columns_Unstockit Inventory Template - Copy.xlsx
+++ b/uploads/extracted_columns_Unstockit Inventory Template - Copy.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,46 +506,48 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>7005</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>543945 2222</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aruba 70051</t>
+          <t>LBB 1990 Plena Voice Alarm1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>www.arubanetworks.com</t>
+          <t>www.belden.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Aruba 7005 Mobility Controller</t>
+          <t>543945 Coax - Surveillance and CCTV Applications</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Belden</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>Mechanical</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>850</v>
+        <v>95</v>
       </c>
       <c r="H2" t="n">
-        <v>510</v>
+        <v>67</v>
       </c>
       <c r="I2" t="n">
-        <v>122</v>
+        <v>30</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>New – Open Box</t>
+          <t>Refurbished / Repaired</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -555,288 +557,20 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Complete Set</t>
+          <t>Missing Accessories</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>365</v>
+        <v>90</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Manufacturer Warranty</t>
+          <t>Distributor Warranty</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>uploads\Aruba 70051.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>3400</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Aruba 34001</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>www.arubanetworks.com</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Aruba 3400 Mobility Controller</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ELV</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>245</v>
-      </c>
-      <c r="H3" t="n">
-        <v>147</v>
-      </c>
-      <c r="I3" t="n">
-        <v>8</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>New – Sealed Box</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Original Packaging</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Complete Set</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>730</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Manufacturer Warranty</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>uploads\Aruba 34001.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AVE-W12S-6015B</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Avoyo cabinet1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>12U Wall mount Cabinet</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Avoyo</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Electrical</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>125</v>
-      </c>
-      <c r="H4" t="n">
-        <v>87</v>
-      </c>
-      <c r="I4" t="n">
-        <v>25</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Like New / Demo</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Repackaged</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Complete Set</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>180</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Distributor Warranty</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>uploads\Avoyo cabinet1.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>9504 060U1000</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>9504 24AWG SHIELDED CABLE ACCESS1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>www.belden.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>9504 Multi-Conductor - Computer Cable for EIA RS-232 Applications</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Belden</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Electrical</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>45</v>
-      </c>
-      <c r="H5" t="n">
-        <v>32</v>
-      </c>
-      <c r="I5" t="n">
-        <v>50</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Used – Fully Functional</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>No Packaging</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Complete Set</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>No Warranty</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>uploads\9504 24AWG SHIELDED CABLE ACCESS1.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>543945 009U1000</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>54394561</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>www.belden.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>543945 Coax - Surveillance and CCTV Applications</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Belden</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Mechanical</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>95</v>
-      </c>
-      <c r="H6" t="n">
-        <v>67</v>
-      </c>
-      <c r="I6" t="n">
-        <v>30</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Refurbished / Repaired</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Original Packaging</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Missing Accessories</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>90</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Distributor Warranty</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>uploads\54394561.pdf</t>
+          <t>uploads\LBB 1990 Plena Voice Alarm1.pdf</t>
         </is>
       </c>
     </row>
